--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -521,41 +521,10 @@
       </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>วางรายละเอียดสินค้าจาก Shopee ทั้งหมดที่นี่</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.lazada.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://down-th.img.susercontent.com/xxx.jpg</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ลด 20%</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="345" customHeight="1">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>RAY-BAN JUSTIN- RB4165F 601/71
 Ray-Ban เรแบนเป็นผู้นำด้านการผลิตแว่นกันแดด และแว่นสายตา ที่ได้ความนิยมมากที่สุดทั่วโลก มีให้เลือกหลากหลายสไตล์ เหมาะกับทุกคน และใส่ได้ทั้งผู้หญิงและผู้ชาย
@@ -569,23 +538,23 @@
 Lens Material: Polycarbonate Standard</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/AUqz80oxUd</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6PzJE?c=b&amp;t=p-ijr1Q-svKWG</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134201-7r990-lscec08f21gm73.webp
 https://down-th.img.susercontent.com/file/th-11134201-7r98y-lscec0amysmu78.webp</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿5,130
 final price indicator icon
@@ -597,17 +566,17 @@
 </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>done 2026-05-21 13:15</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="409.5" customHeight="1">
-      <c r="A4" t="n">
+    <row r="3" ht="345" customHeight="1">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Sony BRAVIA 3 ทีวี 55 นิ้ว รุ่น K-55S30 4K Ultra HD Smart TV (Google TV) | 4K HDR Processor X1
 รายละเอียดสินค้า
@@ -627,22 +596,22 @@
 เรียกดูภาพยนตร์และรายการทีวีมากกว่า 400,000 ตอนจากบริการสตรีมมิ่งของคุณทั้งหมดในที่เดียว โดยจัดเป็นหัวข้อและแนวเนื้อหาไว้ตามสิ่งที่คุณสนใจ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/10zvLKc6Ji</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7r98v-lvsn9yh5vql9c5.webp</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿20,500
 final price indicator icon
@@ -650,6 +619,110 @@
 โค้ดส่วนลดร้านค้า
 ลด ฿1.99k
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ความแปลกใหม่ฟุตบอลซิลิโคนไฟกลางคืนชาร์จโคมไฟกลางคืนนอนพร้อมหรี่แสงได้ 3 ระดับเนอสเซอรี่ข้างเตียงสัมผัสโคมไฟสําหรับตกแต่งห้อง</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4Y0E5z3a</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/sg-11134201-824jf-me523nns7q4g2a.webp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ลด 32% เหลือ ฿359 (ปกติ ฿527)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CODเครื่องลอกเปลือกองุ่นไฟฟ้าอัตโนมัติ เครื่องลอกเปลือกผลไม้โดยไม่ต้องใช้มือ เครื่องเตรียมผลไม้ ช่วยประหยัดแรง</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902Kx1OzPK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/sg-11134201-82593-mgc0wefye8eg8f.webp</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ราคาหลังโค้ดส่วนลด ฿256</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aimi ชุดกันฝน ชุดกันน้ำ เสื้อกันฝน มีแถบสะท้อนแสง รุ่นหมวกติดเสื้อ คุณภาพดีราคาถูกมีหลายสีให้เลือก</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Ax5GMKOTb</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztm-mnjwc17ne13541.webp</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ราคาหลังโค้ดส่วนลด ฿129</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sony BRAVIA 3 ทีวี 55 นิ้ว รุ่น K-55S30 4K Ultra HD Smart TV (Google TV) | 4K HDR Processor X1™</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L92hVfwWK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81zte-mojth82buz2l9f.webp</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ราคาหลังโค้ดส่วนลด ฿20,500</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -621,6 +621,11 @@
 </t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>done 2026-06-01 12:57</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="409.5" customHeight="1">
       <c r="A4" t="n">
@@ -636,7 +641,11 @@
           <t>https://s.shopee.co.th/3B4Y0E5z3a</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/sg-11134201-824jf-me523nns7q4g2a.webp</t>
@@ -662,7 +671,6 @@
           <t>https://s.shopee.co.th/902Kx1OzPK</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/sg-11134201-82593-mgc0wefye8eg8f.webp</t>
@@ -688,7 +696,6 @@
           <t>https://s.shopee.co.th/4Ax5GMKOTb</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-81ztm-mnjwc17ne13541.webp</t>
@@ -714,7 +721,6 @@
           <t>https://s.shopee.co.th/5L92hVfwWK</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-81zte-mojth82buz2l9f.webp</t>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -656,6 +656,11 @@
           <t>ลด 32% เหลือ ฿359 (ปกติ ฿527)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>done 2026-06-03 19:12</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -686,6 +686,11 @@
           <t>ราคาหลังโค้ดส่วนลด ฿256</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 11:49</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -716,6 +716,11 @@
           <t>ราคาหลังโค้ดส่วนลด ฿129</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 11:58</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -746,6 +746,11 @@
           <t>ราคาหลังโค้ดส่วนลด ฿20,500</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 22:48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -752,6 +752,37 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(พร้อมส่งในไทย🇹🇭) รองเท้าวิ่ง ADIDAS ADIZERO EVO SL Size ผู้หญิง รับประกันของแท้ 100% ราคา 7150.00 บาท</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gFqfiwcgV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>45255792167</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mm7fiqcdwd8k65.webp</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>done 2026-06-06 09:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -776,10 +776,36 @@
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mm7fiqcdwd8k65.webp</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>done 2026-06-06 09:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H ราคา 309.00 บาท</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyt87gFze</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:56</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -796,16 +796,41 @@
           <t>https://s.shopee.co.th/9Uyt87gFze</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>done 2026-06-08 07:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>กล่องเก็บของ BOX ความจุสูง กล่องพลาสติก กล่องเก็บของ โปร่งใส เก็บเสื้อผ้า ได้เก็บของเล่น ⚡การลดราคาแบบจำกัดเวลา⚡ ราคา 48.00 บาท</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zuzf4cm4U</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8n40uz26b5a24.webp</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 12:14</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -821,16 +821,141 @@
           <t>https://s.shopee.co.th/9zuzf4cm4U</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8n40uz26b5a24.webp</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>done 2026-06-08 12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>กางเกงขากว้างผ้าไหมน้ำแข็งสีตัดกันสำหรับผู้หญิงฤดูร้อนบาง 2026 กางเกงขายาวทรงตรงเอวสูงเนื้อหลวมใหม่ ราคา 129.00 บาท</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6py7xJRELB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m9ldl588vckgcc.webp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>มู่ลี่ลายไม้ ใบ25mm มู่ลี่ไวนิลพีวีซี ติดตั้งเองได้ง่ายๆ ราคา 222.00 บาท</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P4TOEPJY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mo8ynxdl3rpd91.webp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>46</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HomeHuk โซฟาผ้านั่งพื้น รุ่นมาคุระ ราคา 2190.00 บาท</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9UywdnfDIJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-824h4-mfbpyu64egp7e0.webp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ชุดเซ็ต2ชิ้น เสื้อ McDonald's สีแดง❤️ + กางเกงขาสั้นแต่งแถบ สวยมากๆ ราคาเซล‼️ ราคา 149.00 บาท</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8YzdMsAc</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mo75pagionph41.webp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>57</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>( สินค้า refill จะเป็นเฉพาะน้ำหอมขวดเติม ไม่รวมก้านไม้ ) บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นแบบเติมปริมาณ 385 มล. 1 ชิ้น ราคา 3490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40e05iUPMa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mothc477chsce5.webp</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:04</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -946,16 +946,141 @@
           <t>https://s.shopee.co.th/40e05iUPMa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mothc477chsce5.webp</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>done 2026-06-09 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MNO.9 Hoodie M248 เสื้อฮู้ด สกรีนอก มีกระเป๋าล้วงด้านหน้า GATKE ผ้าสำลีหนานุ่ม เสื้อกันหนาว เสื้อแขนยาว ฮู้ด ราคา 179.00 บาท</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxCiLiHBf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7reoj-m2ca7ylu2juga8.webp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>โต๊ะเขียนหนังสือเด็ก โต๊ะเด็ก70/80cm พร้อมเก้าอี้ เหมาะสำหรับเด็ก ปรับความสูงได้ 82-88 cm ของขวัญ ราคา 669.00 บาท</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V6PRyIUdO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mi2v2967kohv40.webp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ลูกค้าใหม่ 1 บาท 💥💥 เลือก EMS หรือ Kerry เท่านั้น!! ไดร์6268 Cไดร์จัดแต่งทรงผม รุ่น 6268 /PAE3012 -คละสี ราคา 225.00 บาท</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W3uLc4l8v</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m7chjcgtfipr9f.webp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>เบาะรองนั่งเก้าอี้ทาทามิ ลายน่ารัก สไตล์ญี่ปุ่น ราคา 460.00 บาท</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VaGga7r5k</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rblr-ll6se8an5tik29.webp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>กางเกงขากระบอก กางเกงขายาวผู้หญิง ทรงหลวม ปักน้องหมา แมทช์ง่ายมาก สวยแก๋ #111325 ราคา 299.00 บาท</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8YzfZGQa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mhk7v01jq96w91.webp</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:05</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1071,16 +1071,151 @@
           <t>https://s.shopee.co.th/2g8YzfZGQa</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mhk7v01jq96w91.webp</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>done 2026-06-10 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>💥ใหม่💥[มีตะกร้า] ราวตากผ้าสแตนเลส 304 ราวตากผ้าเคลือบสังกะสี ราวแขวนเสื้อผ้า 180*50*150 มีล้อเลื่อนรองรับน้ำหนัก200กก ราคา 239.00 บาท</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P4TJpcnM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-moj2nps9e7t867.webp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>รถไฟฟ้า รถไฟฟ้าพ่วงข้าง มอเตอไซค์ไฟฟ้า (สีเหลือง) ราคา 29900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuDQ9doC3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7932558030</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/c6c31cdd6d511e9b61df3f0aba2d2b41.webp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Adidas F50 Elite Firm Ground Soccer รองเท้าฟุตอบอล【ของแท้ 100%】 ราคา 5760.00 บาท</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiG1zVamT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>50856634972</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mlbxak8wwcn803.webp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>เตียงนอนพับ เตียงนอน เตียงนอนพับได้ หลากหลายฟังก์ชั่น สามารถทำเป็นโซโฟนั่งได้ เตียงพับ ราคา 3298.00 บาท</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fIMq5EJFx</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mgrlmy4ml1ca69.webp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ส่งฟรี‼️Bloom Boom บราอกชิด เก็บทรง ซิลิโคนพรีเมียม ( Premium silicone bra) ราคา 299.00 บาท</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VhfzB9XCL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnl3kp620gzp56.webp</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:16</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1206,16 +1206,146 @@
           <t>https://s.shopee.co.th/3VhfzB9XCL</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnl3kp620gzp56.webp</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>done 2026-06-10 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NEW DROP JINNY PANTS 🤍 กางเกงจินนี่ ราคา 466.00 บาท</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVib1WBWj</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnsgedf6sirs52.webp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spin Mop ชุดถังปั่นสเเตนเลส ชุดถังปั่น ชุดถังไม้ถูพื้นสแตนเลส ไม้ถูพื้น ถังปั่นไม้ม๊อบ ม็อบถูพื้น ชุดถังปั่นม๊อบ ถังปั่น ราคา 145.00 บาท</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxQHwNkZI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mk9glufjk3ya4c.webp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX บด ชง ตีฟองในเครื่องเดียว ราคา 22900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1gEHNf7O</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22478097184</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[ส่งด่วน] Panasonic หม้อตุ๋นไฟฟ้า ขนาด 3.0 ลิตร รุ่น NF-N31AWSN ความร้อน 3 ระดับ ความจุ 3 ลิตร วัสดุเซรามิค ราคา 2250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATLTis532</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0r-mdcojvkm80clc1.webp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SKY Tools เครื่องตัดหญ้าแบตเตอรี่ 12-32V Series เครื่องตัดหญ้า เล็มหญ้า เครื่องเล็มหญ้า ไร้สาย ใช่งานในบ้านน้ำหนักเบา ราคา 313.00 บาท</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VpCItqJB4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul8-lgyjfqcyn9bof7.webp</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1336,16 +1337,146 @@
           <t>https://s.shopee.co.th/2VpCItqJB4</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul8-lgyjfqcyn9bof7.webp</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>มอนอิงข้างเตียง ลายการ์ตูน ใหญ่ หนุนเอว - แพ็คนิ่ม ถอดออกซักได้ ทั้งร้านส่งฟรี(Delin store) ราคา 200.00 บาท</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuEUCNESu</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mehzdrupcuteaf.webp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ADIZERO EVO SL รองเท้าวิ่ง (สินค้าแท้ 100%)JP4149 ราคา 5490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZGs2PTpb</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>48106346968</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-ml0rov1ia0p10d.webp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PRAEWARIN (แพร-วรินทร์) ชุดเดรสผ้าไทยแต่งเข็มกลัดโบว์ ทอลายรวงข้าวแพทเทิร์นสวยหรู ราคา 1445.00 บาท</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4paYBYEO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mo48ye9y93ie73.webp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>L'NADA ชุดเซ็ทลูกไม้ 2 ชิ้น พร้อมกระโปรงดีเทลคาดเอวลูกไม้ (SetscropNew) ราคา 330.00 บาท</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g16BVHINf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-miebjaacynly79.webp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MNO.9 Jeans 5080 กางเกงยีนส์ขายาวชาย เอวยืด มีเชือกรูด ทรงหลวม ราคา 187.00 บาท</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4fWVcJyu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-ls5bmhjwe8xpa2.webp</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:10</t>
         </is>
       </c>
     </row>
@@ -1360,4 +1491,25 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>{"last_personas": ["G", "D", "C", "E", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ"]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1467,16 +1467,141 @@
           <t>https://s.shopee.co.th/3B4fWVcJyu</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-ls5bmhjwe8xpa2.webp</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>done 2026-06-12 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้หญิง สปอร์ตบราคล้องคอ กางเกงเอวสูงขาบาน ฟิตเนส โยคะ พิลาทิส ราคา 690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AptyETiVY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mlj23aw571fm70.webp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>19</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar Light ทรงกลม 68000000W LED พลังงานแสงอาทิตย์ IP69 ป้องกันฟ้าผ่า ราคา 446.00 บาท</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD759gn1Y</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-moyvtydmwzym36.webp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle ฤดูร้อน/ฤดูใบไม้ผลิ สีคากี LK4ED853 ราคา 271.00 บาท</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4paZThz8</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823oo-morz7162e7lud1.webp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Victor พัดลม อุตสาหกรรม 3 ขา รุ่น IF-209B ขนาด 20 นิ้ว สีดำ 5 ใบพัด รับประกันมอเตอร์ 3 ปี พัดลมตั้งพื้น ราคา 1790.00 บาท</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKXq3ih1RH</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/49cd60ad77ea3d3d6d30c6b5ec7c438e.webp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai Berry Powder Feaga Life (ฟีก้าไลฟ์) 80 กรัม พร้อมส่ง ราคา 330.00 บาท</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkU9JmuTA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mgw9302qykuj09.webp</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:33</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R8", "R6", "R7", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1592,16 +1592,141 @@
           <t>https://s.shopee.co.th/LkU9JmuTA</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mgw9302qykuj09.webp</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>done 2026-06-12 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเดียม น้ำจิ้ม คลีน jea ราคา 164.00 บาท</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60OqtkVTFN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mecf64eoeb5w0a.webp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>55</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>9800W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพง ขนาดใบ 16 นิ้ว ระบบน้ำ ไร้ฝุ่น ทำให้การตัดผนังง่ายขึ้น รุ่น รับประกัน ราคา 6889.00 บาท</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1us05IkF</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-ma89t6a7oqkz6c.webp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clinicare IPA 70% *Slim (80 แผ่น) ทิชชู่เปียกฆ่าเชื้อ เกรดโรงพยาบาล HGD Alcohol Wipes กระปุกฟ้า ทิชชู่ [CC-DL0980] ราคา 192.00 บาท</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATLTiSIiJ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23020-fghif5jf3inveb.webp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>32</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>หม้อนึ่งฝาใส 2/3ชั้น ขนาด28cm. หม้อสแตนเลสอเนกประสงค์ ใช้กับเตาแม่เหล็กไฟฟ้าได้ ราคา 93.00 บาท</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbn2NWEBk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lma7as926nim92.webp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ ถูบ้าน ปลอดภัยกับเด็ก และ สัตว์เลี้ยง มิลินคลีน ราคา 294.00 บาท</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOFmpJlfB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1755,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R8", "R6", "R7", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1717,16 +1717,151 @@
           <t>https://s.shopee.co.th/3LOFmpJlfB</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>14</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🔥 กระสอบ 10 kg. 🔥 Mr. Vet T2 สูตรไก่ แซลมอน 10 kg. Hair &amp; Skin อาหารแมว Holistic ผสมฟรีซดราย บำรุงขน ราคา 975.00 บาท</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20sh4LHLuT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>28339554005</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-md3gt3omvexy1a.webp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Salu bare pink (เดรสยาวสาลูสีชมพูอ่อน) ราคา 590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY07jRvCf</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mjve9fy34gld2b.webp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(สินค้าพร้อมส่งในไทย🇹🇭) รองเท้าวิ่ง Adidas Adizero Adios Pro4 ของแท้100% ราคา 7556.00 บาท</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuDQ7iXE9</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>43922252172</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mm7fi69scc20da.webp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>13</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ แต่งลูกไม้ น่ารักมากกกกก ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjCKzTn5Y</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moja5b8vrcowf4.webp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>12</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🫘ธัญพืชรวม 9 เซียน 500 กรัม ไม่ใส่เนย ไม่ใส่น้ำตาล รสธรรมชาติ อบใหม่ทุกวัน ราคา 179.00 บาท</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5QhQsIk6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgg2sb4dc1l899.webp</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1890,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1852,16 +1852,146 @@
           <t>https://s.shopee.co.th/5q5QhQsIk6</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgg2sb4dc1l899.webp</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>14</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>⚡ ลูกค้าใหม่ 1 บาท! พัดลมมือถือเทอร์โบ 💨 ลมแรง 5 ระดับ แบตอึด ใช้งานได้นาน น้ำหนักเบา พกง่าย ส่งด่วนไวทันใจ! ราคา 159.00 บาท</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VoyjJMS7q</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m8vqwsb7876o1f.webp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>33</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ที่นอนยางพาราแท้ 100% 3.5/5/6ฟุต ออกแบบกันลื่น แก้ปวดหลัง พับเก็บได้ หนา สุขภาพ ลาเท็กซ์ Softtopper ราคา 454.00 บาท</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VpCIu6X3s</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-82607-mkbvondaqnm0b5.webp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคา 149.00 บาท</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGmyiFEKo</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnjsnsvs035ud9.webp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>(สินค้าพร้อมส่ง🔥) New Balance 530 รองเท้าผ้าใบ อ่านรายละเอียดก่อนสั่ง‼️ ราคา 3590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyi06G4jp</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22123721647</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m964ckkgi5f26e.webp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>64</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BARCO มู่ลี่ PVC ขนาด 1 นิ้ว สีลายไม้ ราคา 215.00 บาท</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Ab1rYfK33</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m5wkwv1av3bx96.webp</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:51</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2020,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1982,16 +1982,151 @@
           <t>https://s.shopee.co.th/7Ab1rYfK33</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m5wkwv1av3bx96.webp</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>done 2026-06-15 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>20</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Insta360 X5 กล้องแอคชั่น ถ่ายวิดีโอ 8K กันน้ำลึก 15m Sensor 1/1.28" ถ่ายรูป 72MP 360 Action Camera ราคา 20034.00 บาท</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNJTuBIf5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>27133830298</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-men4n13zfuo5cf.webp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>พร้อมส่ง MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ (ลดขนร่วง ลดคราบน้ำตา ลดกลิ่นมูลสัตว์) ทานได้ทุกสายพันธุ์ ราคา 542.00 บาท</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUrFBwwsV0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20348607344</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mopbxox2cfm73f.webp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[48ซอง(ยกลัง)] Pramy อาหารเปียกแมว อาหารลูกแมว อาหารแมวโต อาหารแมวสูงวัย สูตรใหม่ ขนาด 70g ราคา 1060.00 บาท</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEPrP43iz</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul0-lit0litnubgx04.webp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>18</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั้งชุด ราคา 1000.00 บาท</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyt8E3L0m</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-me06n2kwfrbb53.webp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>18</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Philips water Purifier AUT1211 เครื่องกรองน้ําดื่ม UF เครื่องกรองน้ำ กักเก็บแร่ธาตุ ไม่มีน้ำเสีย ราคา 3700.00 บาท</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VoyjJraty</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mokjw6k343yj06.webp</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2155,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2117,16 +2117,141 @@
           <t>https://s.shopee.co.th/2VoyjJraty</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mokjw6k343yj06.webp</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>11</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>【รับประกัน 1 ปี】 TWS หูฟังบลูทูธไร้สาย เสียงดัง คมชัด คุณภาพดี ระบบสัมผัส ใช้งานง่าย ใช้ได้กับ IOS &amp; Android ราคา 56.00 บาท</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VoyjIwfmE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mkkvkc7pmku8d4.webp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>16</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ตู้เชื่อม ตู้เชื่อมไฟฟ้า 2 ระบบ ยี่ห้อ Golden (สายเชื่อมมิก 4 เมตร) รุ่น KTB-MIG/MMA-800 (800AMP) แถมลวด FLUX CORED1ม้วน ราคา 1890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OW6WQcD</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lrvgas8wol7ybf.webp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเมริกัน ทรงเอวต่ำ ทรงหลวม เหมาะสำหรับทุกโอกาส ราคา 125.00 บาท</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P0xlZgh1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260p-mk21nk3nueire4.webp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําหรับผู้ชาย และผู้หญิง 6สี ราคา 17.00 บาท</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPc4cqibS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m23bzo26j8w9b5.webp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>11</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CHUUCHOP - (XS-4XL) Rocky short jeans กางเกงยีนส์ขาสั้นผู้หญิง เอวสูง ผ้ายืด ยีนส์ขาสั้น รับซัมเมอร์ (C9300) ราคา 554.00 บาท</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEZvR5k0j</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0l-mcf7aqssllcseb.webp</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:10</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2280,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2242,16 +2242,145 @@
           <t>https://s.shopee.co.th/AAEZvR5k0j</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0l-mcf7aqssllcseb.webp</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>done 2026-06-17 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>19</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[เลือกรสชาติได้] Purina One อาหารแมว 2.7กก. ราคา 529.00 บาท</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zuzf6Z4y4</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rc-momttucsucqqce.webp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>(ส่งจากกรุงเทพฯ)เสื้อคาร์ดิแกนลําลอง แขนยาว คอปก ติดกระดุม สีพื้น เข้ากับทุกการแต่งกาย สไตล์ใหม่ เสื้อแขนยาวผู้หญิงสไตล์ ราคา 139.00 บาท</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110AwXbVI0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rdwr-lxrx8d94b4kp24.webp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>เครื่องปอกสแตนเลส 3-in-1 สําหรับหั่นและปอกเปลือกสําหรับห้องครัวพร้อมที่จับไม้และที่เปิดขวด ราคา 43.00 บาท</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxQHvsbnA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mmo431l3kutr60.webp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป หม้อนม ชุดหม้อกระทะ ไม่ติดกระทะ ทำความสะอาดง่าย ใช้ได้กับเตาทุกประเภท ราคา 289.00 บาท</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjFqTxEjm</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m9pt2sud0i8f13.webp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>18</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[เลือกรสชาติได้] Purina ONE อาหารแมว 10 kg ราคา 1364.00 บาท</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KfHnpNKJ1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>42922380987</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823q2-momttokhysy74b.webp</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2409,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2377,10 +2377,145 @@
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823q2-momttokhysy74b.webp</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้าเดียว(คิตตี้,คุโรมิ,ชินนาม่อนโรล,มายเมโลดี้)ประกัน 1ปี ราคา 3851.00 บาท</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VaDAxu5GU</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mozceyjaky69f5.webp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>14</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผลิ/ฤดูร้อนสำหรับผู้หญิง L179AD086 ราคา 221.00 บาท</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P0xmml2e</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823qh-morzmx2yxfrg97.webp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>กทม. ส่งใน 2 ชม. ! I WHOOP Peak ,Life 5.0 &amp; MG (ฟรี 12-Month Membership)–Health Fitness Wearable – 24/7 ActivityTracker ราคา 12690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LO4emKNcH</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>27691654401</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mgqjvtnno7pn37.webp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>37</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรงบิด420 Nm บล็อกแบตเตอรี่รุ่นใหม่ สีเทา รุ่น OSID-520 ราคา 980.00 บาท</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KmzFdF3RJ</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0u-mbxidcxyaips95.webp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>16</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>APEX-SX WHITE UP CREAM ครีมทารักแร้ขาว โดยแพทย์ผิวหนังเอเพ็กซ์ ทาขาหนีบดำ แก้มก้นดำ 50 ml. ราคา 891.00 บาท</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSZEmO6NN</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2256012212</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m4rae3s629qi7e.webp</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2544,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2512,10 +2512,145 @@
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m4rae3s629qi7e.webp</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>35</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจากไทย แพ็คเกจอย่างดี ราคา 47.00 บาท</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOJIRGYih</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rbm2-lo3gttrqbnqt55.webp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>23</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม ราคา 715.00 บาท</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5ApxTmaiWR</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RUDY-JEWEL LACE CAMI (สีชมพูพร้อมส่ง)ลูกไม้ติดเพชรทั้งตัวสายปรับไม่ได้ความยาวรวมสาย 18‘ไม่ค่อยยืด ราคา 399.00 บาท</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJlCumsd0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mkhyv58laq6f7c.webp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>17</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer ราคา 6990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pxwpEPQ3n</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>24014645473</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mo6lf69t2mmd04.webp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio สี Midnight Black เครื่องดริปกาแฟ รวม การบด ชั่ง และชง ในเครื่องเดียว ราคา 24500.00 บาท</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyi06j18K</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>27772049148</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2679,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2647,10 +2647,141 @@
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>【1แถม1】🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย หูฟังเกมส์บลูทูธ พร้อมกล่องชาร์จ เหมาะสําหรับ ไอโฟน ซัมซุง oppo vivo ราคา 87.00 บาท</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuEUB54i6</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m0o761t95wig4d.webp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>9</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ”ยกบล๊อก” ราคา 3190.00 บาท</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZGs1e2uE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>44170410987</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mewidulwvd35f3.webp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>27</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ไฟส่องสว่างทางไกล รุ่น VJP-706 ใช้งานได้ยาวนาน กันน้ำได้ ราคา 245.00 บาท</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKZtLFTK3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rcdy-lr5v2ftkd87121.webp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>7</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหรา สวมสบายแต่มีสไตล์สําหรับฤดูใบไม้ผลิ/ฤดูร้อนสําหรับผู้หญิง LK4ED1805 ราคา 314.00 บาท</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDokWlZmU</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823q9-morznv5h67f3a5.webp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>43</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ไม้แขวน ไม้แขวนสูท (ขนาด ยาว 16 นิ้ว สูง 9 นิ้ว บ่ากว้าง 6 เซนติเมตร) สีดำ [คุณภาพดี ราคาประหยัด] ราคา 22.00 บาท</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KmzFeNNhM</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/c3951cba10947d1c5348608b39e86b26.webp</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2810,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "C", "E", "B", "A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2772,16 +2772,146 @@
           <t>https://s.shopee.co.th/8KmzFeNNhM</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/c3951cba10947d1c5348608b39e86b26.webp</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>16</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Choosedress A2032 Penny Mini Cami เสื้อสายเดี่ยว เสื้อสายเดี่ยวลายจุด สกรีนลายหัวใจ ราคา 250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zv9j8kjHA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mp1twlhthn2jd3.webp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>พัดลมพกพา Turbo รอบสูง ชาร์จ USB พัดลมมือถือ Digital Display มือถือพัดลมขนาดเล็ก ปรับระดับได้ 100 ระดับ ราคา 68.00 บาท</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVYWybRCL</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moqjyxd47uvg21.webp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>15</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ผ้าคอตตอนยีนส์ ใส่สบาย พรางต้นขา ใส่ได้ทั้งเอวสูงและเอวต่ำ ราคา 391.00 บาท</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1rMOpXq6</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgq3l3yepamn2a.webp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>6</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>(พร้อมส่ง 1/2วัน) Adidas Adizero EVO SL รองเท้าวิ่ง ผู้ชาย ผู้หญิง (ลิขสิทธิ์แท้ 100%) ราคา 5990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJa4nJcf8</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>26637097078</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mmri6d664cu9ef.webp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>40</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ชั่งได้สูงสุด 40 กก. ซื้อขายได้ มีใบรับรอง / Paveta ราคา 1400.00 บาท</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4Gi24W</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lry0zkbnait9a7.webp</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2940,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "F", "B", "H", "F", "G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R3", "R8", "R6", "R7", "R3", "R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้ ราคาแค่ 690 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ไฟโซล่าเซลล์ UFO ไฟถนนยูเอฟโอ Solar ราคาแค่ 446 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle  ราคาแค่ 271 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Victor พัดลม อุตสาหกรรม ขา ราคาแค่ 1790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผงอาซาอิเบอร์รี่ ผิวสวย Freeze-dried Acai ราคาแค่ 330 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2902,16 +2902,156 @@
           <t>https://s.shopee.co.th/6VLL4Gi24W</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lry0zkbnait9a7.webp</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>13</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>【2026 ผลิตภัณฑ์ใหม่】Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่วงเป็นศูนย์ นวดแผนไทย ถุงลมนิรภัยที่ห่อหุ้มอย่างเ PR30 รุ่นอัปเกรด ราคา 11590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSZEltIuD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5440636974</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mos3jpjkb5ds92.webp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>52</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนกประสงค์พับเก็บได้ ตระกร้าผ้า เอนกประสงค์พับเก็บได้ ความจุขนาดใหญ่ ราคา 105.00 บาท</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdEuo2Kzh</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul0-livcswjzunbl87.webp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>12</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>รุ่นใหม่ล่าสุด 2026 เครื่องทำน้ำแข็ง อัตโนมัติ ice maker ทำน้ำแข็งเร็ว ไม่ละลายใน 5 ชั่วโมง เครื่องทำน้ำแข็งขนาดเล็ก ราคา 2890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V6AoHeJAx</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>44455601920</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mnxxrt37bfuw22.webp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GATORZ - MAGNUM Made In USA รับประกัน Lifetime แว่นทหาร กันแดด ป้องกันสะเก็ด ทหาร Tactical ราคา 7500.00 บาท</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuDQ7Wi7w</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>14694029230</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22100-hdv8fgglhxiv84.webp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>54</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ หลากหลายฟังก์ชั่น สามารถทำเป็นโซโฟนั่งได้ เตียงพับ ราคา 769.00 บาท</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5JQIfQY</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp0laaew2i2qc5.webp</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
         </is>
       </c>
     </row>
@@ -2940,7 +3080,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "A", "G", "F", "F", "B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R5", "R2", "R3", "R8", "R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ เจี๊ยะ น้ำจิ้มสุกี้โบราณ สูตรน้ำตาลน้อย ลดโซเ ราคาแค่ 164 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ W เครื่องตัดผนังคอนกรีต พื้นคอนกรีต ทำลายกำแพ ราคาแค่ 6889 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Clinicare IPA % *Slim ราคาแค่ 192 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ หม้อนึ่งฝาใส ชั้น ขนาด28cm. หม้อสแตนเลสอเนกปร ราคาแค่ 93 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 294 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3042,16 +3042,141 @@
           <t>https://s.shopee.co.th/1gG5JQIfQY</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp0laaew2i2qc5.webp</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CIVAGOxLucky Puppy （26oz/780ml） แก้วกาแฟสแตนเลสซับเซรามิกพร้อมฝาปิดกระติกน้ําสูญญากาศแก้วน้ําร้อนและเย็น ราคา 470.00 บาท</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qRzBsepmP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-ml67nm0lt2q764.webp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>12</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>【UNITED】โคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการควบคุมระยะไกลลดแสงไฟห้องนอนโป๊ะโคมอะคริลิกโปร่งใสสูง ราคา 549.00 บาท</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftgspmQyc</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m0o8zy98y6e046.webp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>45</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ 200 มล. / BsaB Diffuser Oil 200ML 1 ชิ้น ราคา 2690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKZtNy2Ii</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moth7x1nl6o01d.webp</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>10</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer ราคา 6921.00 บาท</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qgyJmjQcx</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mozcimjqsxs236.webp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>36</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>【รับประกัน 20 ปี】กระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไม่ติดกระทะ กระทะเหล็กเผา กระทะเหล็กเผาคลาสสิค กระทะเผาไร้สารกันสนิม ราคา 374.00 บาท</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZVVgWr93</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mma7d0bg55oi0d.webp</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "F", "A", "C", "D", "H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R3", "R8", "R6", "R2", "R4", "R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กระสอบ . 🔥 Mr. ราคาแค่ 975 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Salu bare pink เดรสยาวสาลูสีชมพูอ่อน ราคาแค่ 590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ในไทย🇹🇭 รองเท้าวิ่ง Adidas Adizero ราคาแค่ 7556 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3167,16 +3167,141 @@
           <t>https://s.shopee.co.th/1qZVVgWr93</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mma7d0bg55oi0d.webp</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AOKS🎁ซื้อ 1 แถม 1🎁 เก้าอี้แคมป์ปิ้ง เก้าอี้สนามพับได้ แบบพกพา แถมถุงจัดเก็บ ท่ออลูมิเนียมหนา รับน้ำหนัก300กก ราคา 104.00 บาท</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4BG4y0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m9cv5qevq7m186.webp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>9</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TYESO TS-8829 TS-8830 แก้วน้ําสุญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด 1050 มล. 1200 มล. ราคา 419.00 บาท</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AayLqsNaB</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m8n1ynp79ckycb.webp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>29</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KA Latex ที่นอนยางพาราแท้ รุ่น Sleep Well (ปลอกซิป2ชั้น ถอดซักได้) เหมาะกับผู้มีปันหาปวดหลัง ราคา 1999.00 บาท</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VaGgZQTdD</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23010-87eapdnhunmv8b.webp</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5 ปี】เครื่องตัดหญ้าไฟฟ้า 3980W ไร้สาย มือถือ แบบพกพา มีล้อ เครื่องตัดหญ้าแบต 50000MAH*2 ใช้งานง่าย ฟรี13pcs ราคา 574.00 บาท</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5ApxTjckoC</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-meavz6pq95382b.webp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks หนา 8, 9 นิ้ว [แถมหมอนหนุนเกรดโรงแรม] ราคา 2939.00 บาท</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4BfimK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m2d6ib6zntt00e.webp</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3330,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "A", "H", "H", "E", "B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R5", "R1", "R6", "R4", "R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ที่นอนยางพาราแท้ % ./6ฟุต ออกแบบกันลื่น ราคาแค่ 454 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง ราคาแค่ 149 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔥 New Balance รองเท้าผ้าใบ ราคาแค่ 3590 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BARCO มู่ลี่ PVC ขนาด ราคาแค่ 215 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3292,16 +3292,141 @@
           <t>https://s.shopee.co.th/6VLL4BfimK</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m2d6ib6zntt00e.webp</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>12</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML ราคา 204.00 บาท</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLHYdN6Re</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-ml3hnx0lnuo587.webp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>63</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>【🔥ราคาเคลียร์สต๊อก🔥】ปืนเชื่อมพลาสติก 1600W 220V Heat Air Gunner ถือปืนเชื่อมลมร้อน 40-600 ℃ TPO PVC Vinyl Welding Kit ปรับอุณหภูมิได้ด้วยความเร็วในการเชื่อม เป่าลมร้อน ราคา 2999.00 บาท</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P4TPa4Rb</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-lo10r57h3w637c.webp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer ราคา 6990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110L0VMRke</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mozcimjqsxs236.webp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>15</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เท่า หลายสี ราคา 110.00 บาท</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD75992Gw</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/b33984c4c86bb7bb3f259b7bd8aa3d27.webp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>10</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ดูดยุงร้ายให้ตายในทันที แบบ 360 องศา ปกป้องคนที่คุณรัก โคมดักยุง ราคา 497.00 บาท</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9KAU8uki</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/9db66f2b508e0216fbd10afbdedebe8c.webp</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3455,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "A", "A", "F", "F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R6", "R3", "R2", "R4", "R1", "R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง กล้องแอคชั่น ถ่ายวิดีโอ กันน้ำลึก Sensor ราคาแค่ 20034 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซองยกลัง Pramy อาหารเปียกแมว อาหารลูกแมว ราคาแค่ 1060 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั ราคาแค่ 1000 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Philips water Purifier เครื่องกรองน้ําดื่ม ราคาแค่ 3700 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3417,16 +3417,141 @@
           <t>https://s.shopee.co.th/5L9KAU8uki</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/9db66f2b508e0216fbd10afbdedebe8c.webp</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>11</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TYESO TS-8829 TS-8830 แก้วน้ําสุญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด 1050 มล. 1200 มล. ราคา 419.00 บาท</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5eGyZXM5</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m8n1ynp79ckycb.webp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>18</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>พร้อมส่ง!! FINSSO : ตู้เสื้อผ้า ตู้เสื้อผ้าไม้ คุณภาพดี ราคาถูก แข็งแรง เก็บของได้เยอะ (ตู้เสื้อผ้า 2/3 ประตู wardrobe ราคา 699.00 บาท</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuS3kPA0b</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-lldbgp4ij1z2c1.webp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>30</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพับได้ เบาะพิงหลังเตียง เบาะรองนั่งระเบียง สำหรับการนั่งเป็นเวลานาน ราคา 590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8cVChDaL</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mjz5pj2cxc79b8.webp</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>51</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis MAX หนา 10.5 นิ้ว รุ่น Atlantis Max Hybrid และ Atlantis Max Firm หนา 12 นิ้ว ราคา 15385.00 บาท</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD75EgDJF</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6c5plugo3qvf4.webp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>70</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Alectric เตาย่างไฟฟ้าไร้ควัน 3 in 1 รุ่น SG1-X2 มีระบบโบลเวอร์ดูดควัน - รับประกัน3ปี ราคา 990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqienTzey</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mgqc459wktu2a2.webp</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:44</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3580,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "D", "D", "E", "H", "D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R5", "R8", "R1", "R3", "R1", "R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ตู้เชื่อม ตู้เชื่อมไฟฟ้า ระบบ ยี่ห้อ ราคาแค่ 1890 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น 🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเ ราคาแค่ 125 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ นาฬิกาข้อมือสปอร์ต สีมาการอง สไตล์เกาหลี สําห ราคาแค่ 17 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น CHUUCHOP - XS- Rocky ราคาแค่ 554 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3542,16 +3542,141 @@
           <t>https://s.shopee.co.th/7pqienTzey</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mgqc459wktu2a2.webp</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>done 2026-06-28 05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>22</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ กันฝุ่นและกันน้ำ ตู้เสื้อผ้าพลาสติก'pvc ตู้เสื้อผ้า สไตล์โมเดิร์น ตู้เสื้อผ้าเด็ก ราคา 599.00 บาท</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VhjUia7Q5</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8261d-mjqnv53u8mww58.webp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>39</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู มุ้งกันยุงแบบมีซิป กันแมลง พร้อมม่านเตียงรอบมุ้ง มุ้งกันยุงพับได้ ราคา 698.00 บาท</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OW9vcAu</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mp3cv8iw1jb5fd.webp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>44</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ ถูบ้าน ปลอดภัยกับเด็ก และ สัตว์เลี้ยง มิลินคลีน ราคา 293.00 บาท</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9Ng8dL5u</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>65</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Reunrom รูมดิฟฟิวเซอร์ 200ml สระบุรี ราคา 1043.00 บาท</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902g2vgWY1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m77noa773ju79b.webp</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>69</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hanky House Room &amp; Fabric Spray สเปรย์หอมปรับอากาศ ขนาด 100มล รูมสเปรย์ กลิ่นโรงแรมหรู RoomSpray ราคา 276.00 บาท</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5ApxTtTQA5</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rdvr-mch92x115wgj53.webp</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "A", "A", "C", "H", "G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R7", "R3", "R5", "R6", "R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ของใช้สัตว์เลี้ยงตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เลือกรสชาติได้ Purina One อาหารแมว ราคาแค่ 529 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ส่งจากกรุงเทพฯเสื้อคาร์ดิแกนลําลอง แขนยาว คอป ราคาแค่ 139 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องปอกสแตนเลส -in- สําหรับหั่นและปอกเปลือ ราคาแค่ 43 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดกระทะ กระทะ กระทะก้นลึก หม้อซุป ราคาแค่ 289 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆครับ ตัวนี้มีจุดเด่นคือ เลือกรสชาติได้ Purina ONE อาหารแมว ราคาแค่ 1364 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3667,16 +3667,141 @@
           <t>https://s.shopee.co.th/5ApxTtTQA5</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rdvr-mch92x115wgj53.webp</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>17</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYESO TS-8826 TS-8827 TS-8828 600 มล. 750 มล. 900 มล. แก้วน้ําสูญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด ราคา 329.00 บาท</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG1nlJ22I</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mel4uxcc4hz7fd.webp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>66</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อมโรลเก็บสายปรับระดับน้ำได้10แบบสายยางมี20เมตรกับ10เมตร ราคา 564.00 บาท</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HbfFwJnZ</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/5a8364a936fa3c6acf2d6768fd39c12b.webp</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>11</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TTRacing Duo V4 Chopper One Piece Edition Gaming Chair เก้าอี้สำนักงาน เก้าอี้เกมมิ่ง - รับประกัน 2 ปี ราคา 4821.00 บาท</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6py7xFBexZ</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3thzgdxy4g51.webp</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>20</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML ราคา 223.00 บาท</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbjWmDzqV</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml3hoam25nggae.webp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>59</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>(พร้อมส่ง)บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / 20ขั้น ช่างแอร์ อเนกประสงค์ ยืดได้ พับได้ ราคา 1462.00 บาท</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9NgAiJ2j</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98p-lt7s901y81q5ac.webp</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3830,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "H", "G", "C", "E", "E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R6", "R7", "R1", "R2", "R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3851 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผล ราคาแค่ 221 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น กทม. ส่งใน ชม. ! ราคาแค่ 12690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ OSUKA บล็อกแบตเตอรี่ไร้สาย ไร้แปลงถ่าน 20Vแรง ราคาแค่ 980 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ APEX-SX WHITE UP CREAM ราคาแค่ 891 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3792,16 +3792,141 @@
           <t>https://s.shopee.co.th/5L9NgAiJ2j</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98p-lt7s901y81q5ac.webp</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>3</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>หมอน ErgoLab Deep Sleep หมดปัญหาปวดคอ ไม่ต้องกังวลเรื่องกรน หลับสบายต่อเนื่องตลอดคืน (คืนเงินใน 90 วัน + รับประกัน 1 ปี) ราคา 1411.00 บาท</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fmAZ5DTpk</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>done 2026-07-01 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>60</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>มู่ลี่ไม้ โฟมวูด Foamwood Blinds - A25-24 Butter Milk Color ขนาดใบ 50mm. ราคา 1224.00 บาท</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g19h6wYZK</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mm1lq48d6zuw69.webp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>done 2026-07-01 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>14</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศษ ทนน้ำ ใช้ได้ทั้งแบบดึงด้านล่างและแบบดึงด้านบน เหมาะสำหรับใช้ในบ้าน ราคา 89.00 บาท</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATVXhS24W</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>done 2026-07-01 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>68</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด สไตล์มินิมอล muji (แถมบังราง) ราคา 1199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM6FF5X0S</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qukx-lkimgscnh0bt48.webp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>done 2026-07-01 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>17</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ 600ML/900ML แก้วน้ำเย็น-ร้อน DIY พร้อมหูหิ้ว ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKZtJUmk0</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me5lauh9s8ox03.webp</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>done 2026-07-01 05:56</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3955,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "G", "A", "H", "B", "B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R2", "R4", "R2", "R6", "R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กาวดักแมลงวัน มัดลละ100แผ่น สินค้าพร้อมส่งจาก ราคาแค่ 47 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 715 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ RUDY-JEWEL LACE CAMI สีชมพูพร้อมส่งลูกไม้ติดเ ราคาแค่ 399 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 24500 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3917,16 +3917,141 @@
           <t>https://s.shopee.co.th/3qKZtJUmk0</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me5lauh9s8ox03.webp</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>done 2026-07-01 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>67</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง 200 Bar 950W/4.0HP ปรับแรงดันได้ (มี 3 แบบ) ราคา 1149.00 บาท</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20svi4OUop</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mny382ag7myt04.webp</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>done 2026-07-02 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ แบบพกพา พร้อมปั๊มลมในตัว ที่นอนลม แบบหนา 40/25ซม ราคา 1039.00 บาท</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6fehkvh5FI</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>done 2026-07-02 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>62</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้าเดียว(คิตตี้,คุโรมิ,ชินนาม่อนโรล,มายเมโลดี้)ประกัน 1ปี ราคา 3890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZVVkgn1Q</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mozceyjaky69f5.webp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>done 2026-07-02 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>28</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>❤แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อน ขนาด (22-28cm) กะทะ ไม่ติดกระทะ ทำความสะอาดง่าย ใช้ได้กับเตาทุกประเภท ราคา 219.00 บาท</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY3dHyybG</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lxteh8um0amn62.webp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>done 2026-07-02 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ZINSANO เครื่องฉีดน้ำแรงดันสูง 80-120 บาร์ รุ่น AMAZON ULTRA/ZN1101/FA0803/FA1005 ล้างรถ ดูดฝุ่น ฉีดพื้น รับประกัน 1 ปี ราคา 4290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5JJFrFh</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lpov09alxgxcec.webp</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>done 2026-07-02 05:52</t>
         </is>
       </c>
     </row>
@@ -3955,7 +4080,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "D", "D", "C", "A", "H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R5", "R2", "R5", "R4", "R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 1แถม1🔥NEW🔥 TWSหูฟังบลูทูธ หูฟังบลูทูธไร้สาย ห ราคาแค่ 87 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ การ์ดวันพีชของแท้ เรทคาตั้น พร้อมส่งจากไทยแบบ ราคาแค่ 3190 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ ไฟฉายคาดหัว ไฟส่องกบ ไฟตกปลา ไฟกรีดยาง ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหร ราคาแค่ 314 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ไม้แขวน ไม้แขวนสูท ขนาด ยาว ราคาแค่ 22 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4042,16 +4042,141 @@
           <t>https://s.shopee.co.th/1gG5JJFrFh</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lpov09alxgxcec.webp</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>done 2026-07-02 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>[20ห่อ ] Botare GB/T 20808 Air Cushion Soft Tissue กระดาษทิชชู่ หนา 4 ชั้น 360 แผ่น ราคา 174.00 บาท</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4B8F4b</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m2hsn2b7otuc7a.webp</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>done 2026-07-03 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>13</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SOLOMON ที่นอนยางพารา รุ่น Sunshine ลดแรงกดทับ บอกลาอาการปวดหลัง สัมผัสนุ่มแน่น [แถมหมอน] ราคา 4083.00 บาท</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY3dFUuxo</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6owfzjk0g51d3.webp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>done 2026-07-03 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>42</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DreaME 4 in 1 โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นสูง ด้วยกรอบรูปทรงคงที่ โซฟาปรับนอน สีเบจ Sofa ราคา 5099.00 บาท</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEdR17bPf</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mldc4h2lai9sf9.webp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>done 2026-07-03 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>14</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>โซฟาขี้เกียจ Bean Bag บีนแบ็ก โซฟาหนอนผีเสื้อ พร้อมเม็ดโฟม กันน้ําได้ ถอดออกได้ เก้าอี้เลานจ์ บีนแบก ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80A8qxmfVm</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mibevclvvpxced.webp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>done 2026-07-03 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Maybuck เครื่องตัดหญ้าเบนซิน GX-35 4 จังหวะสำหรับใช้ในครัวเรือน เครื่องตัดหญ้าไร้สายขนาดเล็กเครื่องตัดหญ้าน้ำมันเบนซิน ราคา 2680.00 บาท</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W44PaeA44</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>done 2026-07-03 05:46</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "G", "D", "E", "E", "F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R7", "R5", "R2", "R4", "R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Choosedress Penny Mini Cami ราคาแค่ 250 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลมพกพา Turbo รอบสูง ชาร์จ ราคาแค่ 68 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ราคาแค่ 391 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ วัน Adidas Adizero EVO ราคาแค่ 5990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Accurate เครื่องชั่งดิจิตอล ตราชั่ง คำนวนราคา ราคาแค่ 1400 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4167,16 +4167,141 @@
           <t>https://s.shopee.co.th/W44PaeA44</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>done 2026-07-03 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>6</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บประกอบง่าย ได้ 3/3.5/4/5 ฟุต ด้วยการจัดเก็บ ราคา 2541.00 บาท</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47vAGNeq</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lzifc7rcrpgpdd.webp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>done 2026-07-04 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>8</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม ราคา 675.00 บาท</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdBP86PE9</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>done 2026-07-04 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>61</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic Reed Diffuser ก้านไม้หอมในรูปแบบเซรามิก ราคา 1088.00 บาท</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGqULO84X</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-6byvf8b4tvjv19.webp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>done 2026-07-04 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>13</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TYESO 01-01022/23/24/25/26 600ML/750MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญากาศพร้อมฝาปิด 2-in-1 และฟาง,ถ้วยกาแฟสแตนเลสผนังคู่แก้วเดินทางป้องกันการรั่วพลิก ราคา 339.00 บาท</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJlCpoQ0x</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>done 2026-07-04 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>26</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ 6 ฟุต ราคา 6999.00 บาท</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD75B2ag9</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mny3tn6egdu0e6.webp</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>done 2026-07-04 05:41</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4330,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "A", "G", "H", "D", "H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R4", "R8", "R7", "R5", "R6", "R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ เก้าอี้สุขภาพ ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ผลิตภัณฑ์ใหม่Srabuyเก้าอี้นวด ไฟฟ้า แรงโน้มถ่ ราคาแค่ 11590 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ตะกร้าผ้า ตะกร้าใส่เสื้อผ้าใช้แล้ว ตะกร้าอเนก ราคาแค่ 105 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง GATORZ - MAGNUM Made ราคาแค่ 7500 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ iF เตียงนอนพับ เตียงนอน เตียงนอนพับได้ ราคาแค่ 769 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4292,16 +4292,141 @@
           <t>https://s.shopee.co.th/4qD75B2ag9</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mny3tn6egdu0e6.webp</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>done 2026-07-04 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>24</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ชุดหม้อสแตนเลส 5 ใบ พร้อมฝาปิด ชุดหม้อทำครัว ชุดหม้อต้ม หม้อเอนกประสงค์ ใช้กับเตาไฟฟ้าได้ ขนาด 16/18/20/22/24 ซม สแตนเลส ราคา 143.00 บาท</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8cVBstdM</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m6dx1eebfg8n6b.webp</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>done 2026-07-05 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>41</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ปั๊มลม PUMA 1HP 2สูบ 92L PP21-PPM220V **รับประกัน 1 ปี** ราคา 21550.00 บาท</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4HCtpJ</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98w-luh7frqsr3v912.webp</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>done 2026-07-05 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>48</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื่องฉีดน้ำ ปั้มแรงดันสูงล้างรถ ราคา 1355.00 บาท</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdEunW5zN</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mmficiuh1csj9b.webp</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>done 2026-07-05 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>6</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Mobi GARDEN เก้าอี้ปิกนิก พับได้ แบบพกพา สวยหรู สําหรับตั้งแคมป์กลางแจ้ง ราคา 926.00 บาท</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyt88J1tR</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7qukw-lh7ao27q1gpr5c.webp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>done 2026-07-05 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>3</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5 ปี】เลื่อยไฟฟ้าไร้สาย 12 นิ้ว 55000mAh เลื่อยโซ่ไร้สาย เเลื่อยยนต์ตัดไม้ เลื่อยโซ่ไฟฟ้า เลื่อยไฟฟ้าแบต เลื่อยยนต์ ราคา 964.00 บาท</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g19gyYuOj</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-motibtrh924h09.webp</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>done 2026-07-05 05:38</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4455,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "A", "E", "H", "A", "F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R2", "R6", "R6", "R5", "R1", "R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ CIVAGOxLucky Puppy （/） แก้วกาแฟสแตนเลสซับเซรา ราคาแค่ 470 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ UNITEDโคมไฟตั้งพื้น LED💥ไฟแต่งห้องไฟ ไฟติดการ ราคาแค่ 549 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง บีซาบี น้ำหอมบ้านก้านไม้กระจายกลิ่นปริมาณ มล. ราคาแค่ 2690 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6921 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีกระทะเหล็กเผา สุขภาพดีไม่เคลือบ ไ ราคาแค่ 374 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4417,16 +4417,141 @@
           <t>https://s.shopee.co.th/3g19gyYuOj</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-motibtrh924h09.webp</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>done 2026-07-05 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>19</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่ ราคา 1499.00 บาท</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbjWm5Xax</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>done 2026-07-06 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>53</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>( ลดสูงสุด 50% BsaB โฉมเก่า ซื้อแล้วไม่รับเปลี่ยนคืนทุกกรณี ) BsaB Concentrated Pure Oil / กรุณาอ่านก่อนสั่งซื้อสินค้า ราคา 545.00 บาท</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VpCIx5nlK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m62g8dy5y56ed2.webp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>done 2026-07-06 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>49</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>( ลดสูงสุด 50% BsaB โฉมเก่า ซื้อแล้วไม่รับเปลี่ยนคืนทุกกรณี ) BsaB Diffuser 100ML / กรุณาอ่านก่อนสั่งซื้อสินค้า ราคา 895.00 บาท</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSnsSMQ8j</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m62g7aul5wgta6.webp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>done 2026-07-06 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>9</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>FDM พร้อมส่ง พับได้ มุ้งกันยุง กันแมลง มุ้งเต็นท์ มุ้งครอบผู้ใหญ่และเด็ก 4ฟุต 5ฟุต 6ฟุต 6.6ฟุต ราคา 156.00 บาท</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEdQw2KqE</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-majkutrv8av182.webp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>done 2026-07-06 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>16</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ไม่ต้องเจาะ ที่วางของในห้องน้ำ ชั้นใส่ของ ราคา 169.00 บาท</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80A5LOksuD</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkjqydbkcq9x48.webp</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>done 2026-07-06 05:39</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4580,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "G", "D", "G", "G", "C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R5", "R2", "R3", "R3", "R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี เก้าอี้สุขภาพตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ AOKS🎁ซื้อ แถม 🎁 เก้าอี้แคมป์ปิ้ง ราคาแค่ 104 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น KA Latex ที่นอนยางพาราแท้ รุ่น ราคาแค่ 1999 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องมือช่าง/ทำสวน ดีๆครับ ตัวนี้มีจุดเด่นคือ รับประกัน ปีเครื่องตัดหญ้าไฟฟ้า ไร้สาย มือถือ ราคาแค่ 574 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... เครื่องนอนตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SOLOMON ที่นอนสปริงเกรดโรงแรม รุ่น Cornflaks ราคาแค่ 2939 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4542,16 +4542,66 @@
           <t>https://s.shopee.co.th/80A5LOksuD</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkjqydbkcq9x48.webp</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>done 2026-07-06 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>58</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>เตียงพับได้ 75cm เตียงเสริม เตียงนอนสามารถพับได้ สะดวกในเคลื่อนย้าย เตียงพับ ฟรีที่นอน เก้าอี้พับได้ เตียงสนาม เตียงเดี่ยว ที่นอนพับ เปนอนพับได้ เก้าอี้เอน เตียงผ้าใบ เปลพับ ราคา 810.00 บาท</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fIMq8JLz1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rfie-m419q0lforbr6f.webp</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>done 2026-07-07 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>47</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น P2-0070 (ใส่กระดาษขนาด A5 ได้) ***สีขาว*** ราคา 49.00 บาท</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KfWRUozVV</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23010-ruqywfvz4omv09.webp</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>done 2026-07-07 05:47</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "C", "G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R2", "R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 204 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🔥ราคาเคลียร์สต๊อก🔥ปืนเชื่อมพลาสติก Heat Air G ราคาแค่ 2999 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5"], "recent_captions": ["เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4592,16 +4592,534 @@
           <t>https://s.shopee.co.th/9KfWRUozVV</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-23010-ruqywfvz4omv09.webp</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>done 2026-07-07 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>71</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ แบบพกพา พร้อมปั๊มลมในตัว ที่นอนลม แบบหนา 40/25ซม</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Ld1LV2o10</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>฿829</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>72</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5เเพ็ค กระดาษทิชชู่ Sipeau กระดาษทิชชู่คุณภาพสูง นุ่ม กระดาษทิชชู่เช็ดหน้า</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSaJ9u5pe</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>฿109</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>73</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qRp8GDWdu</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>฿710</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>74</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqV5S2fho</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>฿1499</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>75</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ป้ายฟิวเจอร์บอร์ดคนละครึ่งพลัสขนาด A4 A3ป้ายร้านค้าไทยช่วยไทย</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zuzfR3dRa</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mo3jx74mfdhc39.webp</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>฿69</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>76</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>น้ำยาขจัดคราบน้ำกระจกและหินปูนในห้องน้ำ MARS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxCiiY1UB</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m659yr5og8bu23.webp</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>฿249</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>77</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>【ส่งถึงในวันเดียวกัน】เครื่องตัดหญ้าไฟฟ้า ไร้สาย แบต2ก้อน 50000mah ง่ายต่อการพกพา พับเก็บได้ Lawn mower</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BR3xMw3AR</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbxoukw7r6mr1c.webp</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>฿729</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>78</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>หมอน ErgoLab Deep Sleep หมดปัญหาปวดคอ ไม่ต้องกังวลเรื่องกรน หลับสบายต่อเนื่องตลอดคืน (คืนเงินใน 90 วัน + รับประกัน 1 ปี)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9ALsfuYa4e</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>฿1690</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>79</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDegqiufO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>฿319</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>80</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sipeau 10 แพ็ค กระดาษทิชชู่ กระดาษชําระ หนาเป็นพิเศษ ทนน้ำ ใช้ได้ทั้งแบบดึงด้านล่าง เหมาะสำหรับใช้ได้ทุกที่</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50WJiG0KuX</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm1kxjjdv7db2b.webp</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>฿179</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>81</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Makita เครื่องตัดหญ้าไร้สายแบบ 388Vf เครื่องเล็มหญ้าแบบดูอัลแอคชั่น เครื่องตัดหญ้าในสวน</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W3uLzQXdl</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-maximzfnvalwf1.webp</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>฿1575</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>82</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ZINSANO เครื่องฉีดน้ำแรงดันสูง 80-120 บาร์ รุ่น AMAZON ULTRA/ZN1101/FA0803/FA1005 ล้างรถ ดูดฝุ่น ฉีดพื้น รับประกัน 1 ปี</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VL7V1BXMH</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lpov09alxgxcec.webp</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>฿4620</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>83</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ส่งจากไทย🚚Miffy แก้วกาแฟ มัทฉะ ถ้วยมัทฉะ แก้วน้ำ แก้วการ์ตูน ตกแต่งคาเฟ่ ถ้วยเซรามิก ริเริ่มความคิด</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fm0VUNZsO</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mk0m1nqpb6rl65.webp</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>฿337</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>84</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศษ ทนน้ำ ใช้ได้ทั้งแบบดึงด้านล่างและแบบดึงด้านบน เหมาะสำหรับใช้ในบ้าน</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VoyjfiZOM</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>฿89</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>85</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Maybuck เครื่องตัดหญ้าเบนซิน GX-35 4 จังหวะสำหรับใช้ในครัวเรือน เครื่องตัดหญ้าไร้สายขนาดเล็กเครื่องตัดหญ้าน้ำมันเบนซิน</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftTJegRLc</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>฿2560</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>86</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ZINSANO เครื่องฉีดน้ำแรงดันสูง AD Series 110,140,160,180 บาร์ | Induction motor ทนทาน งานมืออาชีพ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KfIsEam13</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0k-md1hurbdvs918c.webp</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>฿9790</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>87</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>🐕พร้อมส่ง🐶 น้องดัชชุนสุดฮิต DACHSHUND //เขียนการ์ดฟรี 🥺🤎</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1hIirLlu</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/d79d4536e03944c292cfcc00a004b9e9.webp</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>฿889</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>88</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ถังน้ําแข็ง ถังสแตนเลส ถังพักชา ถังน้ําแข็ง6/8/10/12ลิตร ถังชาเก็บความเย็น/ร้อนเก็บชานม ไขมุกน้ำผลไม</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8OvzDDMr</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgn3lu1sly4o99.webp</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>฿389</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>89</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>เครื่องตัดหญ้าสะพายบ่า NIPPON NP35 | NP50MAX2.5HP/ NP35MAX1.8HPครบชุด แถมใบตัด4แบบ ✔ ประกัน1ปี</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VhVvWJjeP</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mop8p3guoi686f.webp</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>฿1896</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>90</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TYESO 01-01022/23/24/25/26 600ML/750MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญากาศพร้อมฝาปิด 2-in-1 และฟาง,ถ้วยกาแฟสแตนเลสผนังคู่แก้วเดินทางป้องกันการรั่วพลิก</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUrGGO0Vle</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>฿349</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4617,7 +4617,6 @@
           <t>https://s.shopee.co.th/1Ld1LV2o10</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</t>
@@ -4626,6 +4625,11 @@
       <c r="F158" t="inlineStr">
         <is>
           <t>฿829</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>done 2026-07-16 22:01</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4647,6 @@
           <t>https://s.shopee.co.th/5VSaJ9u5pe</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</t>
@@ -4669,7 +4672,6 @@
           <t>https://s.shopee.co.th/2qRp8GDWdu</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</t>
@@ -4695,7 +4697,6 @@
           <t>https://s.shopee.co.th/7pqV5S2fho</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</t>
@@ -4721,7 +4722,6 @@
           <t>https://s.shopee.co.th/9zuzfR3dRa</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mo3jx74mfdhc39.webp</t>
@@ -4747,7 +4747,6 @@
           <t>https://s.shopee.co.th/4AxCiiY1UB</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m659yr5og8bu23.webp</t>
@@ -4773,7 +4772,6 @@
           <t>https://s.shopee.co.th/BR3xMw3AR</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbxoukw7r6mr1c.webp</t>
@@ -4799,7 +4797,6 @@
           <t>https://s.shopee.co.th/9ALsfuYa4e</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</t>
@@ -4825,7 +4822,6 @@
           <t>https://s.shopee.co.th/7VDegqiufO</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</t>
@@ -4851,7 +4847,6 @@
           <t>https://s.shopee.co.th/50WJiG0KuX</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm1kxjjdv7db2b.webp</t>
@@ -4877,7 +4872,6 @@
           <t>https://s.shopee.co.th/W3uLzQXdl</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-maximzfnvalwf1.webp</t>
@@ -4903,7 +4897,6 @@
           <t>https://s.shopee.co.th/6VL7V1BXMH</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lpov09alxgxcec.webp</t>
@@ -4929,7 +4922,6 @@
           <t>https://s.shopee.co.th/5fm0VUNZsO</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mk0m1nqpb6rl65.webp</t>
@@ -4955,7 +4947,6 @@
           <t>https://s.shopee.co.th/2VoyjfiZOM</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</t>
@@ -4981,7 +4972,6 @@
           <t>https://s.shopee.co.th/4ftTJegRLc</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</t>
@@ -5007,7 +4997,6 @@
           <t>https://s.shopee.co.th/9KfIsEam13</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0k-md1hurbdvs918c.webp</t>
@@ -5033,7 +5022,6 @@
           <t>https://s.shopee.co.th/6L1hIirLlu</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/d79d4536e03944c292cfcc00a004b9e9.webp</t>
@@ -5059,7 +5047,6 @@
           <t>https://s.shopee.co.th/2g8OvzDDMr</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgn3lu1sly4o99.webp</t>
@@ -5085,7 +5072,6 @@
           <t>https://s.shopee.co.th/3VhVvWJjeP</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mop8p3guoi686f.webp</t>
@@ -5111,7 +5097,6 @@
           <t>https://s.shopee.co.th/AUrGGO0Vle</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</t>
@@ -5148,7 +5133,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R6", "R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5"], "recent_captions": ["เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Ozama บัลลังก์ รุ่น Alpha ราคาแค่ 6990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4657,6 +4657,11 @@
           <t>฿109</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>done 2026-07-17 08:23</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5133,7 +5138,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R7", "R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น ผ้าเช็ดตัวขนเป็ด ลายริ้ว ขนาด70x140ซับนํ้า10เ ราคาแค่ 110 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829"]}</t>
+          <t>{"last_personas": ["E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม"], "last_roles": ["R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4687,6 +4687,11 @@
           <t>฿710</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>done 2026-07-17 19:12</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5138,7 +5143,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม"], "last_roles": ["R4", "R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ราคาแค่ 497 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109"]}</t>
+          <t>{"last_personas": ["A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4717,6 +4717,11 @@
           <t>฿1499</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 18:27</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5143,7 +5148,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R4", "R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO TS- TS- แก้วน้ําสุญญากาศ ราคาแค่ 419 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710"]}</t>
+          <t>{"last_personas": ["B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4747,6 +4747,11 @@
           <t>฿69</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 18:55</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5148,7 +5153,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R5", "R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ !! FINSSO : ตู้เสื้อผ้า ราคาแค่ 699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499"]}</t>
+          <t>{"last_personas": ["A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4777,6 +4777,11 @@
           <t>฿249</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>done 2026-07-20 20:11</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5153,7 +5158,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น AUTU เบาะรองนั่งสำหรับคนขี้เกียจ เสื่อทาทามิพ ราคาแค่ 590 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69"]}</t>
+          <t>{"last_personas": ["A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4807,6 +4807,11 @@
           <t>฿729</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>done 2026-07-21 19:27</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5158,7 +5163,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R4", "R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น SleepHappy ที่นอนยางพาราแท้ รุ่น Atlantis ราคาแค่ 15385 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249"]}</t>
+          <t>{"last_personas": ["F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม"], "last_roles": ["R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1"], "recent_captions": ["ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4837,6 +4837,11 @@
           <t>฿1690</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>done 2026-07-22 19:28</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5163,7 +5168,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม"], "last_roles": ["R4", "R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1"], "recent_captions": ["ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Alectric เตาย่างไฟฟ้าไร้ควัน in รุ่น ราคาแค่ 990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729"]}</t>
+          <t>{"last_personas": ["H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก"], "last_roles": ["R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7"], "recent_captions": ["โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4867,6 +4867,11 @@
           <t>฿319</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>done 2026-07-23 19:26</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5168,7 +5173,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก"], "last_roles": ["R5", "R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7"], "recent_captions": ["โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Living ตู้ใส่เสื้อผ้า พับ ตู้เก็บของ ราคาแค่ 599 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690"]}</t>
+          <t>{"last_personas": ["C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4897,6 +4897,11 @@
           <t>฿179</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>done 2026-07-24 19:23</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5173,7 +5178,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น YYT มุ้งครอบผู้ใหญ่ 10ฟุต สามประตู ราคาแค่ 698 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319"]}</t>
+          <t>{"last_personas": ["H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4927,6 +4927,11 @@
           <t>฿1575</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>done 2026-07-25 19:05</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5178,7 +5183,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R1", "R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ  ราคาแค่ 293 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
+          <t>{"last_personas": ["C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4957,6 +4957,11 @@
           <t>฿4620</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>done 2026-07-26 19:06</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5183,7 +5188,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Reunrom รูมดิฟฟิวเซอร์ สระบุรี ราคา ราคาแค่ 1043 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575"]}</t>
+          <t>{"last_personas": ["C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4987,6 +4987,11 @@
           <t>฿337</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>done 2026-07-27 20:41</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5188,7 +5193,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R8", "R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hanky House Room &amp; ราคาแค่ 276 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620"]}</t>
+          <t>{"last_personas": ["G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม"], "last_roles": ["R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5017,6 +5017,11 @@
           <t>฿89</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>done 2026-07-28 20:07</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5193,7 +5198,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม"], "last_roles": ["R5", "R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TYESO TS- TS- TS- ราคาแค่ 329 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337"]}</t>
+          <t>{"last_personas": ["G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5047,6 +5047,11 @@
           <t>฿2560</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>done 2026-07-29 20:03</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5198,7 +5203,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R1", "R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Uone Garden ชุดอุปกรณ์สายยางรดน้ำต้นไม้ พร้อม ราคาแค่ 564 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89"]}</t>
+          <t>{"last_personas": ["E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5077,6 +5077,11 @@
           <t>฿9790</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>done 2026-07-30 19:48</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5203,7 +5208,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น TTRacing Duo Chopper One ราคาแค่ 4821 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560"]}</t>
+          <t>{"last_personas": ["A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5107,6 +5107,11 @@
           <t>฿889</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>done 2026-07-31 19:59</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5208,7 +5213,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R5", "R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ราคาแค่ 223 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790"]}</t>
+          <t>{"last_personas": ["F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2"], "recent_captions": ["ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5137,6 +5137,11 @@
           <t>฿389</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>done 2026-08-01 19:05</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5213,7 +5218,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2"], "recent_captions": ["ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น บันไดอลูมิเนียมพับได้ แบบ12ขั้น /16ขั้น / ราคาแค่ 1462 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889"]}</t>
+          <t>{"last_personas": ["C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5167,6 +5167,11 @@
           <t>฿1896</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>done 2026-08-02 19:05</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5218,7 +5223,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ หมอน ErgoLab Deep Sleep ราคาแค่ 1411 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389"]}</t>
+          <t>{"last_personas": ["H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม"], "last_roles": ["R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5197,6 +5197,11 @@
           <t>฿349</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>done 2026-08-03 20:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5223,7 +5228,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม"], "last_roles": ["R3", "R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โฟมวูด Foamwood Blinds ราคาแค่ 1224 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896"]}</t>
+          <t>{"last_personas": ["D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5200,6 +5200,1006 @@
       <c r="G177" t="inlineStr">
         <is>
           <t>done 2026-08-03 20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>91</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ถุงสูญญากาศ เก็บเสื้อผ้าผ้าห่มผ้านวมจัดเก็บของกระชับพื้นที่แพ็คของเดินทางถุงใส่เสื้อผ้าพกพา ราคาต่อชิ้น(แบบใส)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AMxjrqLKA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m0pot616b6pmd7.webp</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>฿10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>92</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Goody Home ชั้นวางของแบบวางตั้ง ออกแบบให้ระบายน้ำด้านล่างได้ วางของใช้ในพื้นที่ที่โดนน้ำได้</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/111G0rV7s3</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98t-m03zneg13id66d.webp</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>฿65.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>93</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Deli ถุงคลุมเสื้อผ้า ถุงใส่สูท ที่คลุมเสื้อผ้า มีซิปด้านหน้า หลายขนาด ป้องกันฝุ่น Clothing Dust Bag</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGwo5adCO</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mgw2ykjq12by14.webp</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>฿26.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>94</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Deli ถุงสูญญากาศ 1ใบ มีวาล์ว ถุงเก็บผ้านวม จัดเก็บผ้านวม ประหยัดพื้นที่ สามารถใช้งานซ้ำ Vacuum Bag</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5kaqdeSH</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mgw2x8mi3zewbe.webp</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>฿17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>95</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ถุงคลุมเสื้อผ้า(หนาพิเศษ2ชั้น)กันฝุ่น กันยับแบบมีซิป 4ขนาด ถุงใส่สูท ถุงใส่เสื้อผ้า ที่คลุมเสื้อผ้า Clothing Dust Bag</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGwo5sA40</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-825zq-mlq2ylhwts7779.webp</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>฿21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>96</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ใหม่❗ถุงสูญญากาศ จัดเก็บเสื้อผ้า&amp;ผ้านวม ถุงประหยัดพื้นที่ ถุงสูญญากาศมีวาล์วซิปล็อค2ชั้น หนาพิเศษใช้ซ้ำได้(ราคาต่อ1ใบ)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KvJYVbXRq</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7qul6-li126pfagwwz75.webp</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>฿11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>97</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>🐻💖ถุงสูญญากาศ จัดเก็บผ้านวม ถุงสูญญากาศประหยัดพื้นที่ มีจุกวาล์ว(ราคา1ใบ)💖🐻</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zw4jPZUyo</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7qul4-ljqfd50uri2x8e.webp</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>฿10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>98</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>🥳ถุงสูญญากาศ จัดเก็บเสื้อผ้าผ้านวมเป็นระเบียบ ถุงเก็บผ้านวมมีจุกวาวล์ซิปล็อค2ชั้น ถุงประหยัดพื้นที่จัดเก็บ ลายแบร์บริค🥳</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4fuYNc3DjC</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m0poxd0fdcrc2f.webp</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>฿11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>99</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ถุงสูญญากาศ 1ใบ มีวาล์ว ถุงเก็บผ้านวม ถุงสุญญากาศ จัดเก็บผ้านวม ประหยัดพื้นที่ สามารถใช้งานซ้ำ Storage Vacuum Bag</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxWbnO4iR</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98t-lxw9judbmo4w4f.webp</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>฿9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>100</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ที่วางแก้ว แบบหนีบโต๊ะ ปรับ 3 ระดับ หมุน 360 องศา ประหยัดพื้นที่ เก็บซ่อนใต้โต๊ะ ติดตั้งง่าย พร้อมส่งในไทย!</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80B0Lk7r2g</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mplnq6kpx4wba6.webp</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>฿97.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>101</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ขวดแก้วใส่เครื่องปรุงอาหารพร้อมช้อนตักในตัว ใช้งานง่าย สะดวก จัดเก็บเป็นระเบียบ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fn5ZSKnFY</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-ma8ady0pgs5v65.webp</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>฿14.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>102</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>【มาพร้อมกับ 12 หน้า】สมุดเก็บเอกสาร、แฟ้มจัดเก็บขนาดใหญ่ ที่จัดระเบียบเอกสารครอบครัวหนังหนาพรีเมี่ยมพร้อมกระเป๋าซีลด้านข้างหลายขนาด (A4/B5) หน้าโปร่งใสกันฝุ่นและความชื้นเหมาะสําหรับใบรับรองและไฟล์ส</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pceX7EHSS</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-micqznfxojy955.webp</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>฿69.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>103</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>【จัดส่งที่รวดเร็ว】แผ่นปา DIY แผ่นรูพลาสติกสำหรับจัดเก็บบนโต๊ะพร้อมชุดติดตั้ง ตัวจัดระเบียบโต๊ะเล่นเกม</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KnqkMSrKP</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mlbudatj51xg78.webp</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>฿43.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>104</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Deli ถุงสูญญากาศ ถุงสูญญากาศจัดเก็บของ มีวาล์ว ประหยัดพื้นที่ ใช้งานซ้ำได้ Storage Vacuum Bag</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEjkpaMXa</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mefkkjk10irkb8.webp</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>฿18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>105</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Aimilo ไม้แขวนเสื้อ 8 ตะขอ กันลื่น ประหยัดพื้นที่ ที่เก็บเสื้อผ้า ไม้แขวนผ้าอเนกประสงค์ แขวนสายเดี่ยว/บรา/เข็มขัด</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5LAFAqsRR4</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mp7ec1i114wfab.webp</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>฿16.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>106</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>noordic ชั้นวางของบนโต๊ะ ชั้นเก็บของ 2ชั้น ประหยัดพื้นที่ชั้นวางเดสก์ท็อป ชั้นอเนกประสงค์ สีขาวA1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSuCGAl4V</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-mas1qf3l0nxye7.webp</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>฿67.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>107</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ชั้นเก็บผ้า ลายแพนด้า ที่เก็บถุงเท้า ชุดชั้นใน สามชั้น ถุงเก็บของ ใส่เสื้อผ้า เก็บผ้า ถุงเก็บผ้า เก็บกระเป๋า</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LWdbLKhlZ</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mfnhf8gv711kae.webp</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>฿36.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>108</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ชั้นวางรองเท้า ปรับได้3ระดับ ประหยัดพื้นที่ ที่เก็บรองเท้า อุปกรณ์เก็บรองเท้าพลาสติก พับเก็บได้ ที่จัดระเบียบรองเท้า</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30mKOZMI9J</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7rfgd-m3mzspb77207ff.webp</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>฿8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>109</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>🔥【INS สไตล์】ชั้นวางของบนโต๊ะ ชั้นจัดระเบียบบนโต๊ะทำงาน ชั้นวางอเนกประสงค์ ชั้นวางของ ประหยัดพื้นที่ ติดตั้งง่าย</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Le6PVbVMF</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mitxca7ji80097.webp</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>฿89.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>110</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>กระเป๋าเคลื่อนย้ายความจุขนาดใหญ่ 110ล/180ล/240ล กันน้ําและกันฝุ่นที่ทนทาน เหมาะสําหรับใส่เสื้อผ้าและเครื่องนอน</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pceX8DX6K</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mj50iw22nton7d.webp</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>฿48.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>111</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ผ้าเช็ดกระจกไมโครไฟเบอร์-กระจกอัตโนมัติ ไร้ร่องรอย เช็ด-หนาซุปเปอร์ดูดซับน้ํานํามาใช้ใหม่-ครัวเรือนล้างจานเศษผ้า-ผ้าขนหนูล้างรถมายากล-</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18iobxFlh</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7rdyg-lyasiiofhnvs5f.webp</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>฿5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>112</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>LOGESKI น้ำยาล้างห้องน้ำ ล้างชักโครก ไม่ต้องขัด ขจัดคราบหนัก ตะกรัน คราบเหลือง ดับกลิ่น ฆ่าเชื้อ 99%</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AMxjSRWEV</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mq5ye0zrpf676a.webp</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>฿101.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>113</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>LOGESKI น้ำยาล้างเครื่องซักผ้า ไม่ต้องแช่ ขจัดคราบฝังแน่น ลดกลิ่นอับ ฆ่าเชื้อ 99.9%</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V7GwEd8CN</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-7ras8-mao08sgtxeb04e.webp</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>฿86.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>114</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>LOGESKI น้ำยาล้างห้องน้ำ โฟมทำความสะอาด ไม่ต้องขัด สลายคราบตะกรัน เชื้อรา คราบเหลือง ดับกลิ่น</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18iocHsRA</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mji9ddjg6neufd.webp</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>฿222.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>115</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ผ้าไมโครไฟเบอร์ 3D ขนาด 400แกรม 25X25CM เกรดพรีเมี่ยม หนานุ่ม ซับน้ำไว ทำความสะอาดอเนกประสงค์</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9TzWGf7E</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mnfgv5sgi7t035.webp</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>฿4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>116</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>[ซื้อ 4 แถม 1/3 ถุง ]ผ้าเปียกทำความสะอาดครัว Kiss Aimy กลิ่นเลมอน ขจัดครา</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pz2xB5CTI</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mpf2wiqngidofd.webp</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>฿189.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>117</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Yotex เครื่องปั่นอาหารเด็ก เครื่องปั่นกระเทียม เครื่องปั่น การทำงานด้วยปุ่มเดียว เครื่องปั่นพริก 1000ML ทำความสะอาดง่าย</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LWdauWmR2</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhtuyubih9fn04.webp</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>฿151.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>118</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>(ร้านนี้ส่งไว+ผงข้นฟรี )ไอ-โชว์ หัวเชื้อน้ำยาล้างจานสูตรเข้มข้น ขจัดคราบมัน 8 สูตร 8กลิ่น 400มิล</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEjkPKGDm</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m6qcrl032w1hc1.webp</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>฿21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>119</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BOOMJOY แปรงทําความสะอาดฝักบัวและชุดขัดอ่างอาบน้ํา ด้ามยาว 58 ซม. พร้อมแผ่นใยขัด 2 แผ่น และแผ่นไมโครไฟเบอร์ 1 แผ่น สีเทา</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pra91RRnU</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-7ras8-m3q4rmtmlq2yde.webp</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>฿335.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>120</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Rabito ผลิตภัณฑ์ทำความสะอาดสเปรย์ทำความสะอาดสำหรับผ้า พรม เบาะรถ โซฟา ไม่ต้องใช้น้ำ Cleaning ไม่ต้องเมื่อยขยี้ ไม่ระคายเ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V7GwFXunQ</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mn0veu8izdac3f.webp</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>฿109.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>121</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ROJUKISS Deep Cleansing Micellar Water 400ml โรจูคิส ไมเซล่าวอเตอร์ ทำความสะอาดผิวล้ำลึก สลายเมคอัพ อ่อนโยนต่อผิว</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AbtLni0eu</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-8259w-mqja2tfrz95af7.webp</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>฿129.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>122</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ผ้าไมโครไฟเบอร์ 3D ขนาด 400แกรม 30X30 CM เกรดพรีเมี่ยม หนานุ่ม ซับน้ำไว ทำความสะอาดอเนกประสงค์</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pra91oGrE</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mnfgx95jxret4b.webp</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>฿6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>123</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ฟองน้ําไมโครไฟเบอร์ทําความสะอาดอเนกประสงค์</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/111G0TMKPR</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mhzqlbjyyfb63e.webp</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>฿5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>124</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ถังปั่นไม้ม๊อบ ถังปั่นไม้ถูพื้น Spin Mop ชุดถังปั่นพลาสติก ชุดทำความสะอาดพื้น ไม้ถูพื้น ไม้ม๊อบ ผ้าม๊อบไมโครไฟเบอร์.</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fY9wj6EHF</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m3bulq72u31ka1.webp</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>฿96.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>125</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HOMESTIC ไม้ถูพร้อมถังปั่น ตัวถัง 2 ระบบ ซักทำความสะอาดและปั่นแห้ง ชุดถังปั่นสแตนเลส + ไม้ถูพื้น</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pceWi8Dx7</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mn14s1xi0o3n65.webp</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>฿95.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>126</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>【5KG】Botare ผลิตภัณฑ์ซักผ้ากลิ่นทับทิม หอมยาวนาน ทำความสะอาดล้ำลึก 1ขวด 5000ml</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pk7KsIuCh</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mo3epycylw5c5e.webp</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>฿135.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>127</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>(ซื้อ 3 แถม 2 รวม 400 แผ่น) แผ่นทำความสะอาดครัว ทิชชู่เปียกทำความสะอาด ขจัดคราบน้ำมัน 99% ล้างคราบง่าย</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Le6P5v0sE</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mjqfof7pi3nme2.webp</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>฿157.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>128</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PRO ผลิตภัณฑ์ ล้างจาน โปร ผสมน้ำมะนาว 3,200 ml.</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BS90x87HP</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mkhuf2c7qqklb6.webp</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>฿125.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>129</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Rabito น้ำยาทำความสะอาด คราบมันฝังแน่นห้องครัว น้ำยาขจัดคราบ ห้องครัว ขจัดคราบไขมันในครัว 500มล. C1</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VMCYas7N7</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mi9xmv02k4y099.webp</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>฿91.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>130</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>YTL ลูกกลิ้งกำจัดขน เก็บขนและฝุ่น ลูกกลิ้งทำความสะอาด สีชมพู ขจัดขนแมวและขนสุนัข</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Aqoy968AX</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/add9868da3414a6048e9b9c0ef70c7e9.webp</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>฿4.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5227,6 +5227,11 @@
           <t>฿10.00</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>done 2026-09-12 20:56</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6228,7 +6233,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R8", "R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศ ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349"]}</t>
+          <t>{"last_personas": ["D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ"], "last_roles": ["R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>
